--- a/data/file_generation/input/data_123/总部职能员工1-9月日平均工作小时数统计表_含序号.xlsx
+++ b/data/file_generation/input/data_123/总部职能员工1-9月日平均工作小时数统计表_含序号.xlsx
@@ -16939,13 +16939,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A390B2ED-719E-441F-9227-DD337E4C4C5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{236333DA-D6C2-4281-90E5-A2FE4B8E5963}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51235A8A-B57F-4110-98BF-9F4267651A91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D46ECDBA-C8F8-4E35-89D1-92D3A0A6BF60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F48B113-43F0-4597-BA81-1514CCF7C001}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{554BBD97-7EBB-4E4C-BB82-A3B4DE1772A1}"/>
 </file>